--- a/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près. Papa dit : tu restes avec moi. Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+          <t>Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près. Tu restes avec moi. Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près.
+papa|Tu restes avec moi.
+narrateur|Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Diane est au marché. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Diane reste avec papa. L'accompagnant est là. La main est tenue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Diane et papa rentrent avec les pommes. Ils marchent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Diane est au marché. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Diane reste avec papa. L'accompagnant est là. La main est tenue.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Diane et papa rentrent avec les pommes. Ils marchent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diane reste avec papa au marché</t>
+          <t>La caisse qui sent la pomme</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une caisse sent la pomme. Une feuille reste collée. Nina marche près de papa. Elle reste avec l'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près. Tu restes avec moi. Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+          <t>Une caisse de bois sent la pomme. Le bois est rêche, un peu humide. Une feuille verte reste collée. Elle est sur une pomme rouge. Une flaque brille entre les étals. La balance fait un petit tic. Un sac en papier attend, tout plat. Nina vit ici, avec papa. Papa, ça sent la pomme ! Oui. Les caisses sont pleines. Tu vois la feuille verte ? Oui. Elle est collée. En ce moment, ils marchent entre les étals. Papa tient la main de Nina. La main est chaude. Les pieds de Nina restent près. Papa est l'accompagnant. Nina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils s'arrêtent devant les pommes. Une pomme rouge dépasse. Elle a encore sa petite feuille. Celle-là, papa ! On la prend ensemble. Papa choisit les pommes. Nina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Tu as fait du bon travail. Le sac en papier se froisse. Il fait un bruit de feuille sèche. Ça froisse ! Oui. Le sac est content. Ils écoutent le marchand. La voix est ronde, tout près. Nina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Nina. Papa prend le sac. Le sac pèse un peu. Nina reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. La flaque fait un petit miroir. Les chaussures font un bruit mouillé. Tu tiens encore ma main ? Oui, papa. Bravo. Parce qu'elle reste près, la main est douce. Rester avec l'accompagnant, c'est rester près. Nina est calme. Le sac sent encore le jardin. La feuille verte tremble un peu. On est bien ensemble. Oui. Le marché devient plus calme, derrière eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près.
-papa|Tu restes avec moi.
-narrateur|Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une caisse de bois sent la pomme.
+narrateur|Le bois est rêche, un peu humide.
+narrateur|Une feuille verte reste collée.
+narrateur|Elle est sur une pomme rouge.
+narrateur|Une flaque brille entre les étals.
+narrateur|La balance fait un petit tic.
+narrateur|Un sac en papier attend, tout plat.
+narrateur|Nina vit ici, avec papa.
+enfant-f|Papa, ça sent la pomme !
+papa|Oui.
+papa|Les caisses sont pleines.
+papa|Tu vois la feuille verte ?
+enfant-f|Oui.
+enfant-f|Elle est collée.
+narrateur|En ce moment, ils marchent entre les étals.
+narrateur|Papa tient la main de Nina.
+narrateur|La main est chaude.
+narrateur|Les pieds de Nina restent près.
+narrateur|Papa est l'accompagnant.
+narrateur|Nina aime rester avec l'accompagnant.
+papa|Tu restes avec moi ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu restes avec l'adulte connu.
+narrateur|Ils s'arrêtent devant les pommes.
+narrateur|Une pomme rouge dépasse.
+narrateur|Elle a encore sa petite feuille.
+enfant-f|Celle-là, papa !
+papa|On la prend ensemble.
+narrateur|Papa choisit les pommes.
+narrateur|Nina reste à côté.
+narrateur|Ses pieds restent près des pieds de papa.
+papa|Tu restes bien près.
+papa|Tu as fait du bon travail.
+narrateur|Le sac en papier se froisse.
+narrateur|Il fait un bruit de feuille sèche.
+enfant-f|Ça froisse !
+papa|Oui.
+papa|Le sac est content.
+narrateur|Ils écoutent le marchand.
+narrateur|La voix est ronde, tout près.
+narrateur|Nina reste avec papa.
+narrateur|L'adulte connu reste près.
+enfant-f|Je reste avec l'accompagnant.
+papa|Oui.
+papa|Bravo, Nina.
+narrateur|Papa prend le sac.
+narrateur|Le sac pèse un peu.
+narrateur|Nina reste à côté.
+papa|On rentre ensemble ?
+enfant-f|Oui.
+narrateur|Ils marchent vers la maison.
+narrateur|La flaque fait un petit miroir.
+narrateur|Les chaussures font un bruit mouillé.
+papa|Tu tiens encore ma main ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Parce qu'elle reste près, la main est douce.
+narrateur|Rester avec l'accompagnant, c'est rester près.
+narrateur|Nina est calme.
+narrateur|Le sac sent encore le jardin.
+narrateur|La feuille verte tremble un peu.
+papa|On est bien ensemble.
+enfant-f|Oui.
+narrateur|Le marché devient plus calme, derrière eux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>marche</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Diane est au marché. Que fait-elle ?</t>
+          <t>Nina est au marché. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1580,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Diane est au marché. Que fait-elle ?</t>
+          <t>narrateur|Nina est au marché.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diane reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>Nina reste avec papa. Papa est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Nina. Tu restes avec l'adulte connu. Le sac de pommes pèse encore. La feuille verte est toujours là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1757,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Diane reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>narrateur|Nina reste avec papa.
+narrateur|Papa est l'accompagnant.
+papa|Tu restes avec l'accompagnant ?
+enfant-f|Oui.
+enfant-f|Avec toi.
+papa|Bravo, Nina.
+papa|Tu restes avec l'adulte connu.
+narrateur|Le sac de pommes pèse encore.
+narrateur|La feuille verte est toujours là.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Diane et papa rentrent avec les pommes. Ils marchent ensemble.</t>
+          <t>À la maison, le sac pose un bruit doux. Tu as marché près de moi ? Oui, papa. Bravo. Tu as fait du bon travail. Nina touche une pomme. Elle est lisse, un peu froide. Tu restes avec moi, au marché. Oui. La caisse de bois n'est plus là. Mais l'odeur de pomme reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1933,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Diane et papa rentrent avec les pommes. Ils marchent ensemble.</t>
+          <t>narrateur|À la maison, le sac pose un bruit doux.
+papa|Tu as marché près de moi ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Nina touche une pomme.
+narrateur|Elle est lisse, un peu froide.
+papa|Tu restes avec moi, au marché.
+enfant-f|Oui.
+narrateur|La caisse de bois n'est plus là.
+narrateur|Mais l'odeur de pomme reste.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. C'est du bon travail. La feuille verte repose sur la table. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis restée avec papa.
+papa|Avec l'accompagnant.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|La feuille verte repose sur la table.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une caisse de bois sent la pomme. Le bois est rêche, un peu humide. Une feuille verte reste collée. Elle est sur une pomme rouge. Une flaque brille entre les étals. La balance fait un petit tic. Un sac en papier attend, tout plat. Nina vit ici, avec papa. Papa, ça sent la pomme ! Oui. Les caisses sont pleines. Tu vois la feuille verte ? Oui. Elle est collée. En ce moment, ils marchent entre les étals. Papa tient la main de Nina. La main est chaude. Les pieds de Nina restent près. Papa est l'accompagnant. Nina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils s'arrêtent devant les pommes. Une pomme rouge dépasse. Elle a encore sa petite feuille. Celle-là, papa ! On la prend ensemble. Papa choisit les pommes. Nina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Tu as fait du bon travail. Le sac en papier se froisse. Il fait un bruit de feuille sèche. Ça froisse ! Oui. Le sac est content. Ils écoutent le marchand. La voix est ronde, tout près. Nina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Nina. Papa prend le sac. Le sac pèse un peu. Nina reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. La flaque fait un petit miroir. Les chaussures font un bruit mouillé. Tu tiens encore ma main ? Oui, papa. Bravo. Parce qu'elle reste près, la main est douce. Rester avec l'accompagnant, c'est rester près. Nina est calme. Le sac sent encore le jardin. La feuille verte tremble un peu. On est bien ensemble. Oui. Le marché devient plus calme, derrière eux.</t>
+          <t>Une caisse de bois sent la pomme. Le bois est rêche, un peu humide. Une feuille verte reste collée. Elle est sur une pomme rouge. Une flaque brille entre les étals. La balance fait un petit tic. Un sac en papier attend, tout plat. Nina vit ici, avec papa. Papa, ça sent la pomme ! Oui. Les caisses sont pleines. Tu vois la feuille verte ? Oui. Elle est collée. En ce moment, ils marchent entre les étals. Papa tient la main de Nina. La main est chaude. Les pieds de Nina restent près. Papa est l'accompagnant. Nina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils s'arrêtent devant les pommes. Une pomme rouge dépasse. Elle a encore sa petite feuille. Celle-là, papa ! On la prend ensemble. Papa choisit les pommes. Nina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Le sac en papier se froisse. Il fait un bruit de feuille sèche. Ça froisse ! Oui. Le sac est content. Ils écoutent le marchand. La voix est ronde, tout près. Nina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Nina. Papa prend le sac. Le sac pèse un peu. Nina reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. La flaque fait un petit miroir. Les chaussures font un bruit mouillé. Tu tiens encore ma main ? Oui, papa. Bravo. Parce qu'elle reste près, la main est douce. Rester avec l'accompagnant, c'est rester près. Nina est calme. Le sac sent encore le jardin. La feuille verte tremble un peu. On est bien ensemble. Oui. Le marché devient plus calme, derrière eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane va au marché. Papa vient avec elle. Papa est l'accompagnant. Diane aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des pommes rouges. Diane reste près. Papa dit : tu restes avec moi. Diane hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent le marchand. Diane reste avec papa. L'adulte connu est là. Diane est calme. Elle sourit. Papa prend un sac. Diane reste à côté. Rester avec l'accompagnant, c'est rester près de papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une caisse de bois sent la pomme. Le bois est rêche, un peu humide. Une feuille verte reste collée. Elle est sur une pomme rouge. Une flaque brille entre les étals. La balance fait un petit tic. Un sac en papier attend, tout plat. Nina vit ici, avec papa. Papa, ça sent la pomme ! Oui. Les caisses sont pleines. Tu vois la feuille verte ? Oui. Elle est collée. En ce moment, ils marchent entre les étals. Papa tient la main de Nina. La main est chaude. Les pieds de Nina restent près. Papa est l'accompagnant. Nina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils s'arrêtent devant les pommes. Une pomme rouge dépasse. Elle a encore sa petite feuille. Celle-là, papa ! On la prend ensemble. Papa choisit les pommes. Nina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Le sac en papier se froisse. Il fait un bruit de feuille sèche. Ça froisse ! Oui. Le sac est content. Ils écoutent le marchand. La voix est ronde, tout près. Nina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Nina. Papa prend le sac. Le sac pèse un peu. Nina reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. La flaque fait un petit miroir. Les chaussures font un bruit mouillé. Tu tiens encore ma main ? Oui, papa. Bravo. Parce qu'elle reste près, la main est douce. Rester avec l'accompagnant, c'est rester près. Nina est calme. Le sac sent encore le jardin. La feuille verte tremble un peu. On est bien ensemble. Oui. Le marché devient plus calme, derrière eux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Nina reste à côté.
 narrateur|Ses pieds restent près des pieds de papa.
 papa|Tu restes bien près.
-papa|Tu as fait du bon travail.
 narrateur|Le sac en papier se froisse.
 narrateur|Il fait un bruit de feuille sèche.
 enfant-f|Ça froisse !
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Diane est au marché. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est au marché. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1583,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,7 +1612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Diane reste avec papa. L'accompagnant est là. La &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est tenue.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina reste avec papa. Papa est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Nina. Tu restes avec l'adulte connu. Le sac de pommes pèse encore. La feuille verte est toujours là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,7 +1766,6 @@
 narrateur|La feuille verte est toujours là.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,12 +1790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la maison, le sac pose un bruit doux. Tu as marché près de moi ? Oui, papa. Bravo. Tu as fait du bon travail. Nina touche une pomme. Elle est lisse, un peu froide. Tu restes avec moi, au marché. Oui. La caisse de bois n'est plus là. Mais l'odeur de pomme reste.</t>
+          <t>À la maison, le sac pose un bruit doux. Tu as marché près de moi ? Oui, papa. Bravo. Nina touche une pomme. Elle est lisse, un peu froide. Tu restes avec moi, au marché. Oui. La caisse de bois n'est plus là. Mais l'odeur de pomme reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Diane et papa rentrent avec les pommes. Ils marchent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la maison, le sac pose un bruit doux. Tu as marché près de moi ? Oui, papa. Bravo. Nina touche une pomme. Elle est lisse, un peu froide. Tu restes avec moi, au marché. Oui. La caisse de bois n'est plus là. Mais l'odeur de pomme reste.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1934,6 @@
 papa|Tu as marché près de moi ?
 enfant-f|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Nina touche une pomme.
 narrateur|Elle est lisse, un peu froide.
 papa|Tu restes avec moi, au marché.
@@ -1946,7 +1942,6 @@
 narrateur|Mais l'odeur de pomme reste.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. C'est du bon travail. La feuille verte repose sur la table. L'histoire est finie.</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. La feuille verte repose sur la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. La feuille verte repose sur la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2109,9 @@
           <t>enfant-f|Je suis restée avec papa.
 papa|Avec l'accompagnant.
 papa|Bravo.
-papa|C'est du bon travail.
-narrateur|La feuille verte repose sur la table.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La feuille verte repose sur la table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>marché, caisses de pommes, balance</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diane, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
